--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah Telkom\SEMESTER2\pemodelan basis data\proyek sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25CDC1E9-854D-4BB0-8A4A-6B8E74441B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC59B08-6293-4C88-AEBB-A06AFE076021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5B4922E-FA65-42A9-B4FD-95F19B4F95D4}"/>
   </bookViews>
@@ -371,12 +371,6 @@
     <t>Id_kendaraan</t>
   </si>
   <si>
-    <t>Longitude</t>
-  </si>
-  <si>
-    <t>Latitutde</t>
-  </si>
-  <si>
     <t>ENTITY KOORDINAT</t>
   </si>
   <si>
@@ -564,6 +558,12 @@
   </si>
   <si>
     <t>ENTITY CABANG</t>
+  </si>
+  <si>
+    <t>Longitude (X)</t>
+  </si>
+  <si>
+    <t>Latitutde (Y)</t>
   </si>
 </sst>
 </file>
@@ -601,7 +601,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -633,11 +633,82 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -657,17 +728,53 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1003,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD6CF0B-DAEE-4013-8B7F-BED67DA12E17}">
-  <dimension ref="A1:W57"/>
+  <dimension ref="A1:W87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" customWidth="1"/>
@@ -1025,31 +1132,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="H1" s="7" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="H1" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="Q1" s="7" t="s">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="Q1" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
     </row>
     <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:21" ht="42" thickBot="1" x14ac:dyDescent="0.35">
@@ -3472,35 +3579,35 @@
       </c>
     </row>
     <row r="46" spans="1:23" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="E46" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="I46" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="O46" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="10"/>
-      <c r="T46" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="U46" s="10"/>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="E46" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F46" s="10"/>
+      <c r="G46" s="17"/>
+      <c r="I46" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J46" s="15"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="O46" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="R46" s="9"/>
+      <c r="T46" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
     </row>
     <row r="47" spans="1:23" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
@@ -3515,50 +3622,50 @@
       <c r="E47" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G47" s="2" t="s">
+      <c r="F47" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="J47" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J47" s="1" t="s">
+      <c r="K47" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L47" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="M47" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="O47" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q47" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="P47" s="1" t="s">
+      <c r="R47" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="Q47" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="R47" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="T47" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="U47" s="1" t="s">
         <v>2</v>
       </c>
       <c r="V47" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:23" ht="42" thickBot="1" x14ac:dyDescent="0.35">
@@ -3571,47 +3678,47 @@
       <c r="C48" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="1">
         <v>1</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="12">
         <v>1068456</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="19">
         <v>-62088</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="21">
         <v>1</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="J48" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="M48" s="8">
+      <c r="M48" s="7">
         <v>350000</v>
       </c>
       <c r="O48" s="3">
         <v>101</v>
       </c>
       <c r="P48" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="R48" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="R48" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="T48" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V48" s="3">
         <v>21555123</v>
@@ -3630,47 +3737,47 @@
       <c r="C49" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="12">
+        <v>1068166</v>
+      </c>
+      <c r="G49" s="19">
+        <v>-62146</v>
+      </c>
+      <c r="I49" s="21">
         <v>2</v>
       </c>
-      <c r="F49" s="6">
-        <v>1076191</v>
-      </c>
-      <c r="G49" s="8">
-        <v>-69175</v>
-      </c>
-      <c r="I49" s="3">
-        <v>2</v>
-      </c>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L49" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="M49" s="8">
+      <c r="M49" s="7">
         <v>600000</v>
       </c>
       <c r="O49" s="3">
         <v>102</v>
       </c>
       <c r="P49" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="R49" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="R49" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="T49" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="V49" s="3">
         <v>22444567</v>
@@ -3689,47 +3796,47 @@
       <c r="C50" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="12">
+        <v>1068271</v>
+      </c>
+      <c r="G50" s="19">
+        <v>-61751</v>
+      </c>
+      <c r="I50" s="21">
         <v>3</v>
       </c>
-      <c r="F50" s="6">
-        <v>1127521</v>
-      </c>
-      <c r="G50" s="8">
-        <v>-72575</v>
-      </c>
-      <c r="I50" s="3">
-        <v>3</v>
-      </c>
-      <c r="J50" s="3" t="s">
+      <c r="J50" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K50" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M50" s="8">
+      <c r="M50" s="7">
         <v>900000</v>
       </c>
       <c r="O50" s="3">
         <v>103</v>
       </c>
       <c r="P50" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="R50" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="Q50" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="R50" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="T50" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="V50" s="3">
         <v>31333789</v>
@@ -3748,47 +3855,47 @@
       <c r="C51" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="12">
+        <v>1067891</v>
+      </c>
+      <c r="G51" s="19">
+        <v>-61352</v>
+      </c>
+      <c r="I51" s="21">
         <v>4</v>
       </c>
-      <c r="F51" s="6">
-        <v>1103705</v>
-      </c>
-      <c r="G51" s="8">
-        <v>-77956</v>
-      </c>
-      <c r="I51" s="3">
-        <v>4</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>126</v>
+      <c r="J51" s="14" t="s">
+        <v>124</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="M51" s="8">
+        <v>125</v>
+      </c>
+      <c r="M51" s="7">
         <v>750000</v>
       </c>
       <c r="O51" s="3">
         <v>104</v>
       </c>
       <c r="P51" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="R51" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Q51" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="R51" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="T51" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="V51" s="3">
         <v>27411122</v>
@@ -3807,47 +3914,47 @@
       <c r="C52" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="1">
+        <v>2</v>
+      </c>
+      <c r="F52" s="12">
+        <v>1076191</v>
+      </c>
+      <c r="G52" s="19">
+        <v>-69175</v>
+      </c>
+      <c r="I52" s="21">
         <v>5</v>
       </c>
-      <c r="F52" s="6">
-        <v>1151889</v>
-      </c>
-      <c r="G52" s="8">
-        <v>-84095</v>
-      </c>
-      <c r="I52" s="3">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3" t="s">
+      <c r="J52" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="M52" s="8">
+      <c r="M52" s="7">
         <v>1200000</v>
       </c>
       <c r="O52" s="3">
         <v>105</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="V52" s="3">
         <v>36199988</v>
@@ -3866,41 +3973,41 @@
       <c r="C53" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="1">
+        <v>2</v>
+      </c>
+      <c r="F53" s="12">
+        <v>1075923</v>
+      </c>
+      <c r="G53" s="19">
+        <v>-68914</v>
+      </c>
+      <c r="I53" s="21">
         <v>6</v>
       </c>
-      <c r="F53" s="6">
-        <v>1068456</v>
-      </c>
-      <c r="G53" s="8">
-        <v>-62088</v>
-      </c>
-      <c r="I53" s="3">
-        <v>6</v>
-      </c>
-      <c r="J53" s="3" t="s">
+      <c r="J53" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="L53" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="K53" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="M53" s="8">
+      <c r="M53" s="7">
         <v>300000</v>
       </c>
       <c r="O53" s="3">
         <v>106</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="R53" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:23" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -3913,156 +4020,516 @@
       <c r="C54" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="1">
+        <v>2</v>
+      </c>
+      <c r="F54" s="12">
+        <v>1076100</v>
+      </c>
+      <c r="G54" s="19">
+        <v>-69034</v>
+      </c>
+      <c r="I54" s="21">
         <v>7</v>
       </c>
-      <c r="F54" s="6">
-        <v>1076191</v>
-      </c>
-      <c r="G54" s="8">
-        <v>-69175</v>
-      </c>
-      <c r="I54" s="3">
-        <v>7</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>134</v>
+      <c r="J54" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="M54" s="8">
+        <v>133</v>
+      </c>
+      <c r="M54" s="7">
         <v>350000</v>
       </c>
       <c r="O54" s="3">
         <v>107</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="R54" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:23" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E55" s="3">
+      <c r="E55" s="1">
+        <v>2</v>
+      </c>
+      <c r="F55" s="12">
+        <v>1076432</v>
+      </c>
+      <c r="G55" s="19">
+        <v>-69256</v>
+      </c>
+      <c r="I55" s="21">
         <v>8</v>
       </c>
-      <c r="F55" s="6">
-        <v>1127521</v>
-      </c>
-      <c r="G55" s="8">
-        <v>-72575</v>
-      </c>
-      <c r="I55" s="3">
-        <v>8</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>136</v>
+      <c r="J55" s="14" t="s">
+        <v>134</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="M55" s="8">
+        <v>135</v>
+      </c>
+      <c r="M55" s="7">
         <v>500000</v>
       </c>
       <c r="O55" s="3">
         <v>108</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="R55" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:23" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="3">
+      <c r="E56" s="1">
+        <v>3</v>
+      </c>
+      <c r="F56" s="12">
+        <v>1127521</v>
+      </c>
+      <c r="G56" s="19">
+        <v>-72575</v>
+      </c>
+      <c r="I56" s="21">
         <v>9</v>
       </c>
-      <c r="F56" s="6">
-        <v>1103705</v>
-      </c>
-      <c r="G56" s="8">
-        <v>-77956</v>
-      </c>
-      <c r="I56" s="3">
-        <v>9</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>138</v>
+      <c r="J56" s="14" t="s">
+        <v>136</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="M56" s="8">
+        <v>137</v>
+      </c>
+      <c r="M56" s="7">
         <v>550000</v>
       </c>
       <c r="O56" s="3">
         <v>109</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="R56" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:23" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="3">
+      <c r="E57" s="1">
+        <v>3</v>
+      </c>
+      <c r="F57" s="12">
+        <v>1127944</v>
+      </c>
+      <c r="G57" s="19">
+        <v>-72824</v>
+      </c>
+      <c r="I57" s="22">
         <v>10</v>
       </c>
-      <c r="F57" s="6">
-        <v>1151889</v>
-      </c>
-      <c r="G57" s="8">
-        <v>-84095</v>
-      </c>
-      <c r="I57" s="3">
-        <v>10</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>140</v>
+      <c r="J57" s="14" t="s">
+        <v>138</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="M57" s="8">
+        <v>139</v>
+      </c>
+      <c r="M57" s="7">
         <v>2500000</v>
       </c>
       <c r="O57" s="3">
         <v>110</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R57" s="4" t="s">
-        <v>155</v>
-      </c>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E58" s="1">
+        <v>3</v>
+      </c>
+      <c r="F58" s="12">
+        <v>1127378</v>
+      </c>
+      <c r="G58" s="19">
+        <v>-72458</v>
+      </c>
+      <c r="I58" s="16"/>
+    </row>
+    <row r="59" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E59" s="1">
+        <v>3</v>
+      </c>
+      <c r="F59" s="12">
+        <v>1127500</v>
+      </c>
+      <c r="G59" s="19">
+        <v>-73400</v>
+      </c>
+      <c r="I59" s="16"/>
+    </row>
+    <row r="60" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E60" s="1">
+        <v>4</v>
+      </c>
+      <c r="F60" s="12">
+        <v>1103705</v>
+      </c>
+      <c r="G60" s="19">
+        <v>-77956</v>
+      </c>
+      <c r="I60" s="16"/>
+    </row>
+    <row r="61" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E61" s="1">
+        <v>4</v>
+      </c>
+      <c r="F61" s="12">
+        <v>1103782</v>
+      </c>
+      <c r="G61" s="19">
+        <v>-77828</v>
+      </c>
+      <c r="I61" s="16"/>
+    </row>
+    <row r="62" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E62" s="1">
+        <v>4</v>
+      </c>
+      <c r="F62" s="12">
+        <v>1104262</v>
+      </c>
+      <c r="G62" s="19">
+        <v>-77818</v>
+      </c>
+      <c r="I62" s="16"/>
+    </row>
+    <row r="63" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E63" s="1">
+        <v>4</v>
+      </c>
+      <c r="F63" s="12">
+        <v>1103340</v>
+      </c>
+      <c r="G63" s="19">
+        <v>-77650</v>
+      </c>
+      <c r="I63" s="16"/>
+    </row>
+    <row r="64" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E64" s="1">
+        <v>5</v>
+      </c>
+      <c r="F64" s="12">
+        <v>1151889</v>
+      </c>
+      <c r="G64" s="19">
+        <v>-84095</v>
+      </c>
+      <c r="I64" s="16"/>
+    </row>
+    <row r="65" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E65" s="1">
+        <v>5</v>
+      </c>
+      <c r="F65" s="12">
+        <v>1151628</v>
+      </c>
+      <c r="G65" s="19">
+        <v>-86774</v>
+      </c>
+      <c r="I65" s="16"/>
+    </row>
+    <row r="66" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E66" s="1">
+        <v>5</v>
+      </c>
+      <c r="F66" s="12">
+        <v>1152625</v>
+      </c>
+      <c r="G66" s="19">
+        <v>-86705</v>
+      </c>
+      <c r="I66" s="16"/>
+    </row>
+    <row r="67" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E67" s="1">
+        <v>5</v>
+      </c>
+      <c r="F67" s="12">
+        <v>1151740</v>
+      </c>
+      <c r="G67" s="19">
+        <v>-87467</v>
+      </c>
+      <c r="I67" s="16"/>
+    </row>
+    <row r="68" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E68" s="1">
+        <v>6</v>
+      </c>
+      <c r="F68" s="12">
+        <v>1068456</v>
+      </c>
+      <c r="G68" s="19">
+        <v>-62088</v>
+      </c>
+      <c r="I68" s="16"/>
+    </row>
+    <row r="69" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E69" s="1">
+        <v>6</v>
+      </c>
+      <c r="F69" s="12">
+        <v>1069001</v>
+      </c>
+      <c r="G69" s="19">
+        <v>-62500</v>
+      </c>
+      <c r="I69" s="16"/>
+    </row>
+    <row r="70" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E70" s="1">
+        <v>6</v>
+      </c>
+      <c r="F70" s="12">
+        <v>1068000</v>
+      </c>
+      <c r="G70" s="19">
+        <v>-63000</v>
+      </c>
+      <c r="I70" s="16"/>
+    </row>
+    <row r="71" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E71" s="1">
+        <v>6</v>
+      </c>
+      <c r="F71" s="12">
+        <v>1067005</v>
+      </c>
+      <c r="G71" s="19">
+        <v>-61500</v>
+      </c>
+      <c r="I71" s="16"/>
+    </row>
+    <row r="72" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E72" s="1">
+        <v>7</v>
+      </c>
+      <c r="F72" s="12">
+        <v>1076191</v>
+      </c>
+      <c r="G72" s="19">
+        <v>-69175</v>
+      </c>
+      <c r="I72" s="16"/>
+    </row>
+    <row r="73" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E73" s="1">
+        <v>7</v>
+      </c>
+      <c r="F73" s="12">
+        <v>1076600</v>
+      </c>
+      <c r="G73" s="19">
+        <v>-69500</v>
+      </c>
+      <c r="I73" s="16"/>
+    </row>
+    <row r="74" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E74" s="1">
+        <v>7</v>
+      </c>
+      <c r="F74" s="12">
+        <v>1075500</v>
+      </c>
+      <c r="G74" s="19">
+        <v>-68800</v>
+      </c>
+      <c r="I74" s="16"/>
+    </row>
+    <row r="75" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E75" s="1">
+        <v>7</v>
+      </c>
+      <c r="F75" s="12">
+        <v>1077000</v>
+      </c>
+      <c r="G75" s="19">
+        <v>-69200</v>
+      </c>
+      <c r="I75" s="16"/>
+    </row>
+    <row r="76" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E76" s="1">
+        <v>8</v>
+      </c>
+      <c r="F76" s="12">
+        <v>1127521</v>
+      </c>
+      <c r="G76" s="19">
+        <v>-72575</v>
+      </c>
+      <c r="I76" s="16"/>
+    </row>
+    <row r="77" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E77" s="1">
+        <v>8</v>
+      </c>
+      <c r="F77" s="12">
+        <v>1126500</v>
+      </c>
+      <c r="G77" s="19">
+        <v>-72000</v>
+      </c>
+      <c r="I77" s="16"/>
+    </row>
+    <row r="78" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E78" s="1">
+        <v>8</v>
+      </c>
+      <c r="F78" s="12">
+        <v>1128000</v>
+      </c>
+      <c r="G78" s="19">
+        <v>-73000</v>
+      </c>
+      <c r="I78" s="16"/>
+    </row>
+    <row r="79" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E79" s="1">
+        <v>8</v>
+      </c>
+      <c r="F79" s="12">
+        <v>1127200</v>
+      </c>
+      <c r="G79" s="19">
+        <v>-72800</v>
+      </c>
+      <c r="I79" s="16"/>
+    </row>
+    <row r="80" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E80" s="1">
+        <v>9</v>
+      </c>
+      <c r="F80" s="12">
+        <v>1103705</v>
+      </c>
+      <c r="G80" s="19">
+        <v>-77956</v>
+      </c>
+      <c r="I80" s="16"/>
+    </row>
+    <row r="81" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E81" s="1">
+        <v>9</v>
+      </c>
+      <c r="F81" s="12">
+        <v>1104000</v>
+      </c>
+      <c r="G81" s="19">
+        <v>-78500</v>
+      </c>
+      <c r="I81" s="16"/>
+    </row>
+    <row r="82" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E82" s="1">
+        <v>9</v>
+      </c>
+      <c r="F82" s="12">
+        <v>1102500</v>
+      </c>
+      <c r="G82" s="19">
+        <v>-77000</v>
+      </c>
+      <c r="I82" s="16"/>
+    </row>
+    <row r="83" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E83" s="1">
+        <v>9</v>
+      </c>
+      <c r="F83" s="12">
+        <v>1105000</v>
+      </c>
+      <c r="G83" s="19">
+        <v>-78000</v>
+      </c>
+      <c r="I83" s="16"/>
+    </row>
+    <row r="84" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E84" s="1">
+        <v>10</v>
+      </c>
+      <c r="F84" s="12">
+        <v>1151889</v>
+      </c>
+      <c r="G84" s="19">
+        <v>-84095</v>
+      </c>
+      <c r="I84" s="16"/>
+    </row>
+    <row r="85" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E85" s="1">
+        <v>10</v>
+      </c>
+      <c r="F85" s="12">
+        <v>1151000</v>
+      </c>
+      <c r="G85" s="19">
+        <v>-85000</v>
+      </c>
+      <c r="I85" s="16"/>
+    </row>
+    <row r="86" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E86" s="1">
+        <v>10</v>
+      </c>
+      <c r="F86" s="12">
+        <v>1154000</v>
+      </c>
+      <c r="G86" s="19">
+        <v>-83500</v>
+      </c>
+      <c r="I86" s="16"/>
+    </row>
+    <row r="87" spans="5:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E87" s="1">
+        <v>10</v>
+      </c>
+      <c r="F87" s="12">
+        <v>1152000</v>
+      </c>
+      <c r="G87" s="20">
+        <v>-88000</v>
+      </c>
+      <c r="I87" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
